--- a/Excel/Ejercicios/05- datos.xlsx
+++ b/Excel/Ejercicios/05- datos.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuria López Álvarez\git\Excel_Avanzado\Ejercicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Excel-PowerBI\Excel\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEDED60-048D-4E03-91E6-2DD419BFC20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E04EED-11B9-42BA-9F21-C64998BBCE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2845" yWindow="-12545" windowWidth="22326" windowHeight="11946" xr2:uid="{40CB655C-ABCD-4368-9B71-D8236957EB31}"/>
+    <workbookView xWindow="-24154" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{40CB655C-ABCD-4368-9B71-D8236957EB31}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cifra de ventas" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>JULIO</t>
   </si>
@@ -65,78 +65,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Mall: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mallorca</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Men e In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Menorca e Ibiza</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Península</t>
-    </r>
-  </si>
-  <si>
     <t>DECORACIÓ</t>
   </si>
   <si>
@@ -153,31 +81,25 @@
   </si>
   <si>
     <t>ÁRBOLES CHINOS</t>
+  </si>
+  <si>
+    <t>Mall: Mallorca</t>
+  </si>
+  <si>
+    <t>Men e In: Menorca e Ibiza</t>
+  </si>
+  <si>
+    <t>PE: Península</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -203,10 +125,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -231,9 +151,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -271,7 +191,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -377,7 +297,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -519,7 +439,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -527,86 +447,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C0C9B0-CB72-4F19-B3B9-B8FBCDF983F3}">
-  <dimension ref="A1:T18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.8984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" customWidth="1"/>
-    <col min="3" max="3" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="19" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.19921875" style="1"/>
+    <col min="14" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2"/>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3"/>
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -661,7 +549,6 @@
       <c r="S3" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -721,7 +608,6 @@
       <c r="S4">
         <v>46410</v>
       </c>
-      <c r="T4"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -781,7 +667,6 @@
       <c r="S5">
         <v>41480</v>
       </c>
-      <c r="T5"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -841,167 +726,20 @@
       <c r="S6">
         <v>43110</v>
       </c>
-      <c r="T6"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7"/>
-      <c r="T7"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8"/>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9"/>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10"/>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="T11"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14"/>
-      <c r="T14"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
